--- a/quizzes/sculpture-15e-niveau1.xlsx
+++ b/quizzes/sculpture-15e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{192E8711-0AD8-4F75-BD07-87322F0DF50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD075E4E-B13F-4F88-92EF-BD970791EE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="224">
   <si>
     <t>image</t>
   </si>
@@ -37,6 +37,15 @@
     <t>titre de l'œuvre</t>
   </si>
   <si>
+    <t>dates artiste</t>
+  </si>
+  <si>
+    <t>Matériaux et technique</t>
+  </si>
+  <si>
+    <t>Dimensions</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/db/Milano_-_Agostino_di_Duccio_%281418-1481%29_-_Allegoria_-_dal_Tempio_Malatestiano_-_Foto_Giovanni_Dall%27Orto_-_6-jan-2007_-_02.jpg/1280px-Milano_-_Agostino_di_Duccio_%281418-1481%29_-_Allegoria_-_dal_Tempio_Malatestiano_-_Foto_Giovanni_Dall%27Orto_-_6-jan-2007_-_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -52,6 +61,15 @@
     <t>Allégorie (reliefs du Tempio Malatestiano)</t>
   </si>
   <si>
+    <t>1418-1481</t>
+  </si>
+  <si>
+    <t>Marbre</t>
+  </si>
+  <si>
+    <t>reliefs (dimensions architecturales)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Desiderio_da_settignano%2C_marietta_strozzi%2C_1460_circa%2C_da_berlino_staatliche_museen-bode_museum.JPG/1280px-Desiderio_da_settignano%2C_marietta_strozzi%2C_1460_circa%2C_da_berlino_staatliche_museen-bode_museum.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -67,6 +85,12 @@
     <t>Buste de Marietta Strozzi</t>
   </si>
   <si>
+    <t>1430-1464</t>
+  </si>
+  <si>
+    <t>buste, environ 52 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/26/Bust_of_Piero_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Piero_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -82,6 +106,12 @@
     <t>Buste de Piero de Médicis</t>
   </si>
   <si>
+    <t>1429-1484</t>
+  </si>
+  <si>
+    <t>buste, environ 51 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Francesco_Laurana%2C_Busto_di_donna%2C_quasi_certamente_di_Eleonora_d%27Aragona%2C_1489-91_-FG1.jpg/1280px-Francesco_Laurana%2C_Busto_di_donna%2C_quasi_certamente_di_Eleonora_d%27Aragona%2C_1489-91_-FG1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -97,6 +127,12 @@
     <t>Buste d'Éléonore d'Aragon</t>
   </si>
   <si>
+    <t>vers 1430-vers 1502</t>
+  </si>
+  <si>
+    <t>buste, environ 43 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/13/Nicolaus_von_Leyden%2C_Self-portrait.JPG/1280px-Nicolaus_von_Leyden%2C_Self-portrait.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -112,6 +148,15 @@
     <t>Buste d'homme accoudé (autoportrait présumé)</t>
   </si>
   <si>
+    <t>vers 1420-1473</t>
+  </si>
+  <si>
+    <t>Grès polychrome</t>
+  </si>
+  <si>
+    <t>buste, environ 45 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Benedetto_da_maiano%2C_pulpito_di_s._croce_08.JPG/1280px-Benedetto_da_maiano%2C_pulpito_di_s._croce_08.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -127,6 +172,12 @@
     <t>Chaire de Santa Croce</t>
   </si>
   <si>
+    <t>1442-1497</t>
+  </si>
+  <si>
+    <t>chaire (dimensions architecturales)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/Altare_maggiore_del_duomo_di_siena_02.JPG/1280px-Altare_maggiore_del_duomo_di_siena_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -142,6 +193,15 @@
     <t>Ciboire en bronze du maître-autel</t>
   </si>
   <si>
+    <t>1410-1480</t>
+  </si>
+  <si>
+    <t>Bronze doré</t>
+  </si>
+  <si>
+    <t>ciboire (dimensions architecturales)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG/1280px-Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -157,6 +217,15 @@
     <t>Compianto sul Cristo morto</t>
   </si>
   <si>
+    <t>vers 1435-1494</t>
+  </si>
+  <si>
+    <t>Terre cuite polychrome</t>
+  </si>
+  <si>
+    <t>groupe grandeur nature</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Modena%2C_San_Giovanni_Battista%2C_Compianto_sul_Cristo_Morto_by_Guido_Mazzoni_004.JPG/1280px-Modena%2C_San_Giovanni_Battista%2C_Compianto_sul_Cristo_Morto_by_Guido_Mazzoni_004.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -172,6 +241,9 @@
     <t>Compianto sul Cristo morto (groupe en terre cuite polychrome)</t>
   </si>
   <si>
+    <t>vers 1450-1518</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg/1280px-David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -184,6 +256,15 @@
     <t>David (bronze)</t>
   </si>
   <si>
+    <t>1435-1488</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+  </si>
+  <si>
+    <t>126 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/Bronze_David_by_Donatello-Bargello.jpg/1280px-Bronze_David_by_Donatello-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -193,6 +274,12 @@
     <t>vers 1440</t>
   </si>
   <si>
+    <t>vers 1386-1466</t>
+  </si>
+  <si>
+    <t>158 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d9/%28Venice%29_Davide_con_la_testa_di_Golia%2C_fine_secolo_XV_-_Museo_Correr.jpg/1280px-%28Venice%29_Davide_con_la_testa_di_Golia%2C_fine_secolo_XV_-_Museo_Correr.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -208,6 +295,12 @@
     <t>David avec la tête de Goliath (bronze)</t>
   </si>
   <si>
+    <t>vers 1437-1497</t>
+  </si>
+  <si>
+    <t>environ 47 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -223,6 +316,12 @@
     <t>La Cantoria</t>
   </si>
   <si>
+    <t>1399-1482</t>
+  </si>
+  <si>
+    <t>tribune (dimensions architecturales)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg/1280px-Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -238,6 +337,12 @@
     <t>La Fonte Gaia</t>
   </si>
   <si>
+    <t>vers 1374-1438</t>
+  </si>
+  <si>
+    <t>fontaine monumentale (dimensions architecturales)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9e/Firenze_Battistero_Porta_Ghiberti_detta_del_Paradiso.jpg/1280px-Firenze_Battistero_Porta_Ghiberti_detta_del_Paradiso.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -250,6 +355,12 @@
     <t>La Porte du Paradis</t>
   </si>
   <si>
+    <t>1378-1455</t>
+  </si>
+  <si>
+    <t>porte, environ 5,2 × 2,9 m</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/30/N%C3%BCrnberg_St._Lorenz_Sakramentshaus_Adam_Kraft_01.jpg/1280px-N%C3%BCrnberg_St._Lorenz_Sakramentshaus_Adam_Kraft_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -265,6 +376,15 @@
     <t>Le Ciboire (Sakramentshaus)</t>
   </si>
   <si>
+    <t>vers 1460-1509</t>
+  </si>
+  <si>
+    <t>Pierre</t>
+  </si>
+  <si>
+    <t>ciboire, environ 18,7 m de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Dijon_%28C%C3%B4te-d%27Or%29_-_Puits_de_Mo%C3%AFse_-_Isa%C3%AFe.jpg/1280px-Dijon_%28C%C3%B4te-d%27Or%29_-_Puits_de_Mo%C3%AFse_-_Isa%C3%AFe.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -280,6 +400,15 @@
     <t>Le Puits de Moïse (détail : le prophète Isaïe)</t>
   </si>
   <si>
+    <t>vers 1340-1405</t>
+  </si>
+  <si>
+    <t>Pierre calcaire polychrome</t>
+  </si>
+  <si>
+    <t>statue, environ 195 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7f/Bertoldo_di_giovanni%2C_orfeo_o_apollo%2C_1475-80_01.JPG/1280px-Bertoldo_di_giovanni%2C_orfeo_o_apollo%2C_1475-80_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -292,6 +421,12 @@
     <t>Orphée ou Apollon (statuette en bronze)</t>
   </si>
   <si>
+    <t>vers 1440-1491</t>
+  </si>
+  <si>
+    <t>statuette, environ 40 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/23/Chiesa_San_Domenico_%28Palermo%29_Pieta_von_Domenico_Gagini.jpg/1280px-Chiesa_San_Domenico_%28Palermo%29_Pieta_von_Domenico_Gagini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -307,6 +442,12 @@
     <t>Pietà</t>
   </si>
   <si>
+    <t>vers 1420-1492</t>
+  </si>
+  <si>
+    <t>groupe (dimensions architecturales)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9c/Hochaltar_von_Veit_Sto%C3%9F%2C_Marienkirche%2C_Krakau%2C_Polen.JPG/1280px-Hochaltar_von_Veit_Sto%C3%9F%2C_Marienkirche%2C_Krakau%2C_Polen.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -322,6 +463,39 @@
     <t>Retable de l'église Notre-Dame</t>
   </si>
   <si>
+    <t>vers 1447-1533</t>
+  </si>
+  <si>
+    <t>Bois polychrome doré</t>
+  </si>
+  <si>
+    <t>retable, environ 13 m de haut</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6c/Tilman_Riemenschneider_Magdalena_BNM_img01.jpg/1280px-Tilman_Riemenschneider_Magdalena_BNM_img01.jpg</t>
+  </si>
+  <si>
+    <t>Tilman RIEMENSCHNEIDER</t>
+  </si>
+  <si>
+    <t>1490-1492</t>
+  </si>
+  <si>
+    <t>Bayerisches Nationalmuseum, Munich</t>
+  </si>
+  <si>
+    <t>Retable de Sainte-Madeleine (Münnerstadt Altar)</t>
+  </si>
+  <si>
+    <t>vers 1460-1531</t>
+  </si>
+  <si>
+    <t>Bois polychrome</t>
+  </si>
+  <si>
+    <t>retable (dimensions architecturales)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Francesco_di_giorgio_martini%2C_san_cristoforo%2C_1488-90%2C_da_s._agostino_a_siena.JPG/1280px-Francesco_di_giorgio_martini%2C_san_cristoforo%2C_1488-90%2C_da_s._agostino_a_siena.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -337,6 +511,15 @@
     <t>Saint Christophe (bois polychrome et doré)</t>
   </si>
   <si>
+    <t>1439-1501</t>
+  </si>
+  <si>
+    <t>Bois polychrome et doré</t>
+  </si>
+  <si>
+    <t>statue, environ 190 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8a/Cartuja_de_Miraflores_%28Burgos%29_-_Tumba_de_Juan_II.jpg/1280px-Cartuja_de_Miraflores_%28Burgos%29_-_Tumba_de_Juan_II.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -352,6 +535,15 @@
     <t>Tombeau de Jean II de Castille et Isabelle de Portugal</t>
   </si>
   <si>
+    <t>actif 1475-1505 (dates incertaines)</t>
+  </si>
+  <si>
+    <t>Albâtre</t>
+  </si>
+  <si>
+    <t>tombeau monumental (dimensions architecturales)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Bruni_Santa_Croce_01.JPG/1280px-Bruni_Santa_Croce_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -364,6 +556,9 @@
     <t>Tombeau de Leonardo Bruni</t>
   </si>
   <si>
+    <t>1409-1464</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fc/Tomba_di_Pietro_da_Noceto_segretario_di_Niccol%C3%B2_V%2C_opera_di_Matteo_Civitali_%281472%29.JPG/1280px-Tomba_di_Pietro_da_Noceto_segretario_di_Niccol%C3%B2_V%2C_opera_di_Matteo_Civitali_%281472%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -379,6 +574,9 @@
     <t>Tombeau de Pietro da Noceto</t>
   </si>
   <si>
+    <t>1436-1501</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Cappella_del_cardinale_di_portogallo_03_tomba_del_cardinale_di_antonio_e_bernardo_rossellino_05.JPG/1280px-Cappella_del_cardinale_di_portogallo_03_tomba_del_cardinale_di_antonio_e_bernardo_rossellino_05.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -394,6 +592,9 @@
     <t>Tombeau du cardinal de Portugal (Jacques de Lusitanie)</t>
   </si>
   <si>
+    <t>1427-1479</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/84/Dodici_Apostoli_Pietro_Riario_1.jpg/1280px-Dodici_Apostoli_Pietro_Riario_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -409,6 +610,9 @@
     <t>Tombeau du cardinal Pietro Riario</t>
   </si>
   <si>
+    <t>1418-1503</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Pietro_Lombardo_-_Monumento_del_doge_Pietro_Mocenigo_-_Venezia-SS_Giovanni_e_Paolo.JPG/1280px-Pietro_Lombardo_-_Monumento_del_doge_Pietro_Mocenigo_-_Venezia-SS_Giovanni_e_Paolo.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -424,6 +628,9 @@
     <t>Tombeau du doge Pietro Mocenigo</t>
   </si>
   <si>
+    <t>vers 1435-1515</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/69/Grabmaljohannes13.jpg/1280px-Grabmaljohannes13.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -439,6 +646,12 @@
     <t>Tombeau du pape (anti-pape) Jean XXIII (avec Donatello)</t>
   </si>
   <si>
+    <t>1396-1472</t>
+  </si>
+  <si>
+    <t>Bronze et marbre</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ea/Tesoro_di_san_pietro%2C_tomba_di_sisto_IV_di_antonio_del_pollaiolo%2C_01.JPG/1280px-Tesoro_di_san_pietro%2C_tomba_di_sisto_IV_di_antonio_del_pollaiolo%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -454,6 +667,9 @@
     <t>Tombeau du pape Sixte IV</t>
   </si>
   <si>
+    <t>vers 1431-1498</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/13/Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_06.JPG/1280px-Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_06.JPG</t>
   </si>
   <si>
@@ -469,38 +685,26 @@
     <t>Tondi des Innocents (terre cuite vernissée)</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6c/Tilman_Riemenschneider_Magdalena_BNM_img01.jpg/1280px-Tilman_Riemenschneider_Magdalena_BNM_img01.jpg</t>
-  </si>
-  <si>
-    <t>Tilman RIEMENSCHNEIDER</t>
-  </si>
-  <si>
-    <t>1490-1492</t>
-  </si>
-  <si>
-    <t>Bayerisches Nationalmuseum, Munich</t>
-  </si>
-  <si>
-    <t>Retable de Sainte-Madeleine (Münnerstadt Altar)</t>
+    <t>1435-1525</t>
+  </si>
+  <si>
+    <t>Terre cuite vernissée</t>
+  </si>
+  <si>
+    <t>tondi, environ 145 cm de diamètre chacun</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Carlito"/>
     </font>
     <font>
       <sz val="11"/>
@@ -512,8 +716,22 @@
       <color rgb="FF0563C1"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -522,8 +740,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC54F38"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor rgb="FFC54F38"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -585,22 +815,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -903,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.28515625" customWidth="1"/>
@@ -911,556 +1148,972 @@
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="45" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+    <col min="7" max="7" width="24.42578125" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" ht="30" customHeight="1">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="4" t="s">
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="F6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="G6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="H6" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="4" t="s">
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="4" t="s">
+      <c r="F7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="G7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="4" t="s">
+      <c r="F8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="G8" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="H8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="D9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="E9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="F9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="G9" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="4" t="s">
+      <c r="H9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="F10" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="G10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="D11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="F11" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="G11" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="H11" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="4" t="s">
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="G12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="4" t="s">
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="D13" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="F13" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="G13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="D14" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="E14" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="F14" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="G14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="D22" s="4" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" t="s">
-        <v>144</v>
-      </c>
-      <c r="B32" t="s">
-        <v>145</v>
-      </c>
-      <c r="C32" t="s">
-        <v>146</v>
-      </c>
-      <c r="D32" t="s">
-        <v>147</v>
-      </c>
-      <c r="E32" t="s">
-        <v>148</v>
-      </c>
+      <c r="E22" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E32">
-    <sortCondition ref="E32"/>
-  </sortState>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
